--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-21).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-21).xlsx
@@ -912,17 +912,17 @@
   </si>
   <si>
     <t>214
-165</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>R$ 541.939,72</t>
-  </si>
-  <si>
-    <t>R$ 3.061,81
-R$ 3.130,84</t>
+168</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 549.858,15</t>
+  </si>
+  <si>
+    <t>R$ 3.054,77
+R$ 3.122,07</t>
   </si>
   <si>
     <t>(14.3%)
@@ -932,13 +932,13 @@
     <t>35.3</t>
   </si>
   <si>
-    <t>(15.3%)</t>
-  </si>
-  <si>
-    <t>205.3%</t>
-  </si>
-  <si>
-    <t>158.8%</t>
+    <t>(15.2%)</t>
+  </si>
+  <si>
+    <t>203.4%</t>
+  </si>
+  <si>
+    <t>157.0%</t>
   </si>
   <si>
     <t>4.4%</t>
@@ -950,10 +950,10 @@
     <t>25.7</t>
   </si>
   <si>
-    <t>76.7%</t>
-  </si>
-  <si>
-    <t>7.2%</t>
+    <t>76.0%</t>
+  </si>
+  <si>
+    <t>7.1%</t>
   </si>
   <si>
     <t>4.6</t>
@@ -968,10 +968,13 @@
     <t>17.6</t>
   </si>
   <si>
+    <t>76.8%</t>
+  </si>
+  <si>
     <t>-R$ 15.749,60</t>
   </si>
   <si>
-    <t>2.94</t>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2210,10 +2213,10 @@
         <v>0.042553191489361764</v>
       </c>
       <c r="T7" s="6">
-        <v>0.41980999739318187</v>
+        <v>0.41100596125186289</v>
       </c>
       <c r="U7" s="6">
-        <v>0.065570475080294913</v>
+        <v>0.056766438938975865</v>
       </c>
       <c r="V7" s="6">
         <v>0.062031572009659981</v>
@@ -8643,7 +8646,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8679,25 +8682,59 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>3495.5100000000002</v>
+      </c>
+      <c r="P58" s="5">
+        <v>3495.5100000000002</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.0040147025302027517</v>
+      </c>
+      <c r="R58" s="7">
+        <v>47</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.20512820512820507</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.26906960643797323</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.08494168232961713</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.008194512388750139</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.016262576848585755</v>
+      </c>
+      <c r="X58" s="8">
+        <v>27.263977419354841</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>3.3507400000000001</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.8086032258064515</v>
+      </c>
       <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>18.794087096774195</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.67741935483870963</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -14782,10 +14819,10 @@
         <v>-0.22580645161290325</v>
       </c>
       <c r="T107" s="6">
-        <v>-27.826684495693247</v>
+        <v>-26.16217116934191</v>
       </c>
       <c r="U107" s="6">
-        <v>-28.151582437429202</v>
+        <v>-26.487069111077865</v>
       </c>
       <c r="V107" s="6">
         <v>0.024001859490884219</v>
@@ -16758,7 +16795,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -22873,7 +22910,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>44</v>
@@ -22909,25 +22946,61 @@
       <c t="s" r="N172" s="4">
         <v>52</v>
       </c>
-      <c r="O172" s="5"/>
-      <c r="P172" s="5"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="7"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="8"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-      <c r="AA172" s="8"/>
-      <c r="AB172" s="8"/>
-      <c r="AC172" s="8"/>
-      <c r="AD172" s="8"/>
-      <c r="AE172" s="6"/>
+      <c r="O172" s="5">
+        <v>1544.3</v>
+      </c>
+      <c r="P172" s="5">
+        <v>1544.3</v>
+      </c>
+      <c r="Q172" s="6">
+        <v>-0.15878177787219672</v>
+      </c>
+      <c r="R172" s="7">
+        <v>19</v>
+      </c>
+      <c r="S172" s="6">
+        <v>-0.050000000000000044</v>
+      </c>
+      <c r="T172" s="6">
+        <v>0.2220266787541281</v>
+      </c>
+      <c r="U172" s="6">
+        <v>-0.047344557404649358</v>
+      </c>
+      <c r="V172" s="6">
+        <v>0.059149452826523341</v>
+      </c>
+      <c r="W172" s="6">
+        <v>-0.024370588616201515</v>
+      </c>
+      <c r="X172" s="8">
+        <v>27.162500000000001</v>
+      </c>
+      <c r="Y172" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="Z172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="8">
+        <v>3.9271947368421052</v>
+      </c>
+      <c r="AB172" s="8">
+        <v>6.71875</v>
+      </c>
+      <c r="AC172" s="8">
+        <v>10.395833</v>
+      </c>
+      <c r="AD172" s="8">
+        <v>17.329168750000001</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>0.8125</v>
+      </c>
       <c r="AF172" s="9"/>
-      <c r="AG172" s="5"/>
+      <c r="AG172" s="5">
+        <v>0</v>
+      </c>
       <c r="AH172" s="10">
         <v>1</v>
       </c>
@@ -25752,7 +25825,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25788,25 +25861,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>2878.6199999999999</v>
+      </c>
+      <c r="P195" s="5">
+        <v>2878.6199999999999</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>-0.21607703556849411</v>
+      </c>
+      <c r="R195" s="7">
+        <v>34</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.26086956521739135</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.34516643391625151</v>
+      </c>
+      <c r="U195" s="6">
+        <v>0.0084877476012811693</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.044988049829432164</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0064244325405923676</v>
+      </c>
+      <c r="X195" s="8">
+        <v>23.18405652173913</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.56521739130434778</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>5.1057281249999997</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>3.9586956521739127</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>15.848552173913044</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>1</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>0</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -28200,17 +28307,17 @@
         <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -28220,10 +28327,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-21).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-21).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-168</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 549.858,15</t>
-  </si>
-  <si>
-    <t>R$ 3.054,77
-R$ 3.122,07</t>
-  </si>
-  <si>
-    <t>(14.3%)
-(13.1%)</t>
-  </si>
-  <si>
-    <t>35.3</t>
-  </si>
-  <si>
-    <t>(15.2%)</t>
-  </si>
-  <si>
-    <t>203.4%</t>
-  </si>
-  <si>
-    <t>157.0%</t>
+171</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 561.978,13</t>
+  </si>
+  <si>
+    <t>R$ 3.070,92
+R$ 3.138,17</t>
+  </si>
+  <si>
+    <t>(14.2%)
+(13.0%)</t>
+  </si>
+  <si>
+    <t>35.5</t>
+  </si>
+  <si>
+    <t>(15.3%)</t>
+  </si>
+  <si>
+    <t>198.0%</t>
+  </si>
+  <si>
+    <t>151.9%</t>
   </si>
   <si>
     <t>4.4%</t>
@@ -950,16 +950,16 @@
     <t>25.7</t>
   </si>
   <si>
-    <t>76.0%</t>
-  </si>
-  <si>
-    <t>7.1%</t>
+    <t>75.7%</t>
+  </si>
+  <si>
+    <t>7.0%</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>6.4</t>
+    <t>6.3</t>
   </si>
   <si>
     <t>11.1</t>
@@ -968,10 +968,10 @@
     <t>17.6</t>
   </si>
   <si>
-    <t>76.8%</t>
-  </si>
-  <si>
-    <t>-R$ 15.749,60</t>
+    <t>76.7%</t>
+  </si>
+  <si>
+    <t>-R$ 16.132,15</t>
   </si>
   <si>
     <t>2.95</t>
@@ -2947,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2983,25 +2983,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>5584.54</v>
+      </c>
+      <c r="P13" s="5">
+        <v>5584.54</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.096764906628367009</v>
+      </c>
+      <c r="R13" s="7">
+        <v>66</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.13157894736842102</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.38755310195647269</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.06212253829321663</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.029811461642319691</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.026221192792960566</v>
+      </c>
+      <c r="X13" s="8">
+        <v>25.156209803921566</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>4.437313432835821</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>5.5127450980392156</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>9.8018470000000004</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>16.705554901960785</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.78431372549019607</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-59.850000000000001</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -5670,10 +5706,10 @@
         <v>-0.035714285714285698</v>
       </c>
       <c r="T34" s="6">
-        <v>0.32049705262757688</v>
+        <v>0.42528560393052117</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.052978496537636678</v>
+        <v>0.051810054765307582</v>
       </c>
       <c r="V34" s="6">
         <v>0.13053775073403484</v>
@@ -6634,7 +6670,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6670,25 +6706,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>2130.6100000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>2130.6100000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.09726035523015375</v>
+      </c>
+      <c r="R42" s="7">
+        <v>21</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.30000000000000004</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.053440047685873994</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.2680969769221021</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.055599570076175366</v>
+      </c>
+      <c r="W42" s="6">
+        <v>-0.0086496355503822842</v>
+      </c>
+      <c r="X42" s="8">
+        <v>24.692158823529411</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.2587285714285716</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>5.13958125</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>12.127818</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>18.485294117647058</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.70588235294117652</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -8724,7 +8796,9 @@
       <c r="AB58" s="8">
         <v>7.8086032258064515</v>
       </c>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>11.857526</v>
+      </c>
       <c r="AD58" s="8">
         <v>18.794087096774195</v>
       </c>
@@ -10908,7 +10982,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10942,25 +11016,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>4404.8299999999999</v>
+      </c>
+      <c r="P76" s="5">
+        <v>4404.8299999999999</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.055750391219533069</v>
+      </c>
+      <c r="R76" s="7">
+        <v>53</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.25352112676056338</v>
+      </c>
+      <c r="T76" s="6">
+        <v>-1.84957696437774</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-2.2474424892674634</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.024797438266630039</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.018407407323324625</v>
+      </c>
+      <c r="X76" s="8">
+        <v>26.277776666666668</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.7336471698113205</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>4.079332</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>7.8887770000000002</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>15.708333333333334</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-322.69999999999999</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -20743,7 +20853,7 @@
         <v>0.01607527346377427</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.027160373210883691</v>
+        <v>-0.028396643657256228</v>
       </c>
       <c r="X154" s="8">
         <v>19.448715384615387</v>
@@ -23901,7 +24011,9 @@
       <c r="AB179" s="8">
         <v>1.861904761904762</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>5.4992049999999999</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.444442857142857</v>
       </c>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-21).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-21).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-171</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 561.978,13</t>
-  </si>
-  <si>
-    <t>R$ 3.070,92
-R$ 3.138,17</t>
-  </si>
-  <si>
-    <t>(14.2%)
-(13.0%)</t>
-  </si>
-  <si>
-    <t>35.5</t>
-  </si>
-  <si>
-    <t>(15.3%)</t>
-  </si>
-  <si>
-    <t>198.0%</t>
-  </si>
-  <si>
-    <t>151.9%</t>
+173</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 567.610,58</t>
+  </si>
+  <si>
+    <t>R$ 3.068,17
+R$ 3.134,45</t>
+  </si>
+  <si>
+    <t>(14.4%)
+(13.2%)</t>
+  </si>
+  <si>
+    <t>35.4</t>
+  </si>
+  <si>
+    <t>(15.6%)</t>
+  </si>
+  <si>
+    <t>194.8%</t>
+  </si>
+  <si>
+    <t>148.8%</t>
   </si>
   <si>
     <t>4.4%</t>
@@ -959,7 +959,7 @@
     <t>4.6</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.4</t>
   </si>
   <si>
     <t>11.1</t>
@@ -968,13 +968,13 @@
     <t>17.6</t>
   </si>
   <si>
-    <t>76.7%</t>
-  </si>
-  <si>
-    <t>-R$ 16.132,15</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>76.5%</t>
+  </si>
+  <si>
+    <t>-R$ 16.370,85</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -4384,7 +4384,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4420,25 +4420,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>3054.5799999999999</v>
+      </c>
+      <c r="P24" s="5">
+        <v>3054.5799999999999</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-0.23101826677139348</v>
+      </c>
+      <c r="R24" s="7">
+        <v>33</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.2978723404255319</v>
+      </c>
+      <c r="T24" s="6">
+        <v>-0.0053166065383784345</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.33361051273824877</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.084262320842799998</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.0085694268933863248</v>
+      </c>
+      <c r="X24" s="8">
+        <v>29.407142857142855</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.4479156249999998</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>12.015433333333332</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>21.580953571428573</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.4642857142857143</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-71.799999999999997</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -12600,7 +12634,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12639,7 +12673,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12673,25 +12707,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>2577.8699999999999</v>
+      </c>
+      <c r="P89" s="5">
+        <v>2577.8699999999999</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.41623791882172845</v>
+      </c>
+      <c r="R89" s="7">
+        <v>23</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-2.7741581227912966</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-3.1363098216744834</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.050581681776039909</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.013236897128249291</v>
+      </c>
+      <c r="X89" s="8">
+        <v>28.104545454545452</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>4.8812500000000005</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>6.463636363636363</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>19.962118181818184</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.72727272727272729</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-166.90000000000001</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16643,7 +16711,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18606,7 +18674,7 @@
         <v>-92.599999999999994</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20884,7 +20952,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
